--- a/survey_templates/028_immunoglobulin_a_nephropathy_survey--survey_templates.xlsx
+++ b/survey_templates/028_immunoglobulin_a_nephropathy_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'a_little'}</t>
+          <t>a_little</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'A little'}</t>
+          <t>A little</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'moderately'}</t>
+          <t>moderately</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Moderately'}</t>
+          <t>Moderately</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'severely'}</t>
+          <t>severely</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Severely'}</t>
+          <t>Severely</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_1_month'}</t>
+          <t>less_than_1_month</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 1 month'}</t>
+          <t>Less than 1 month</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'1-3_months'}</t>
+          <t>1-3_months</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': '1-3 months'}</t>
+          <t>1-3 months</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'4-6_months'}</t>
+          <t>4-6_months</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': '4-6 months'}</t>
+          <t>4-6 months</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_6_months'}</t>
+          <t>more_than_6_months</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'More than 6 months'}</t>
+          <t>More than 6 months</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'medical_care'}</t>
+          <t>medical_care</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Medical care'}</t>
+          <t>Medical care</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'emotional_support'}</t>
+          <t>emotional_support</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Emotional support'}</t>
+          <t>Emotional support</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'clinic'}</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Clinic'}</t>
+          <t>Clinic</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'specialist'}</t>
+          <t>specialist</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Specialist'}</t>
+          <t>Specialist</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'hospital'}</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Hospital'}</t>
+          <t>Hospital</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Family'}</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'friend'}</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Friend'}</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
